--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487731_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487731_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1653</v>
+        <v>6.425</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0344</v>
+        <v>4.7301</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1309</v>
+        <v>1.6949</v>
       </c>
       <c r="G2" t="n">
         <v>2.8719</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>7.9337</v>
+        <v>3.1934</v>
       </c>
       <c r="T2" t="n">
-        <v>6.7966</v>
+        <v>2.4924</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1371</v>
+        <v>0.701</v>
       </c>
       <c r="V2" t="n">
         <v>0.9418</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6251</v>
+        <v>3.9923</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>1.9925</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1251</v>
+        <v>1.9998</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6106</v>
+        <v>-1.3013</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9499</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6607</v>
+        <v>-0.3431</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5585</v>
+        <v>-1.0643</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7209</v>
+        <v>0.2019</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1624</v>
+        <v>-1.2662</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0521</v>
+        <v>-0.2369</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.229</v>
+        <v>-1.16</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8231000000000001</v>
+        <v>0.9231</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3582</v>
+        <v>2.5224</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5523</v>
+        <v>3.4926</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9607</v>
+        <v>1.7261</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2525</v>
+        <v>0.9673</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2918</v>
+        <v>0.7588</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0833</v>
+        <v>1.0451</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.0597</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0833</v>
+        <v>-2.0146</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1027</v>
+        <v>1.4934</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1301</v>
+        <v>1.2593</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9726</v>
+        <v>0.2341</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3013</v>
+        <v>-1.6106</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-0.9499</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3431</v>
+        <v>-0.6607</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0643</v>
+        <v>-0.5585</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2019</v>
+        <v>-0.7209</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2662</v>
+        <v>0.1624</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2369</v>
+        <v>-1.0521</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.16</v>
+        <v>-0.229</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9231</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4926</v>
+        <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1635</v>
+        <v>1.829</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8951</v>
+        <v>2.0118</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7315</v>
+        <v>-0.1828</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0451</v>
+        <v>-0.0833</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0597</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0146</v>
+        <v>-0.0833</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5183</v>
+        <v>1.1226</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1887</v>
+        <v>-2.2425</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6704</v>
+        <v>3.3651</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5564</v>
+        <v>-1.1153</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-2.9049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2847</v>
+        <v>1.7897</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1713</v>
+        <v>-1.5512</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3336</v>
+        <v>-1.8784</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1624</v>
+        <v>0.3271</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3852</v>
+        <v>0.436</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5075</v>
+        <v>-1.0266</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1223</v>
+        <v>1.4626</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>1.3582</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>3.2985</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7775</v>
+        <v>1.9047</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7362</v>
+        <v>1.2491</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0413</v>
+        <v>0.6556</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1033</v>
+        <v>-1.025</v>
       </c>
       <c r="W5" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6848</v>
+        <v>-1.025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0561</v>
+        <v>1.1117</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02</v>
+        <v>1.8094</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0362</v>
+        <v>-0.6977</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2988</v>
+        <v>-0.5564</v>
       </c>
       <c r="H6" t="n">
-        <v>0.061</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3598</v>
+        <v>0.2847</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6267</v>
+        <v>-0.1713</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.3336</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6267</v>
+        <v>0.1624</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3279</v>
+        <v>-0.3852</v>
       </c>
       <c r="N6" t="n">
-        <v>0.061</v>
+        <v>-0.5075</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2669</v>
+        <v>0.1223</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2427</v>
+        <v>1.3708</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6068</v>
+        <v>1.3568</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3641</v>
+        <v>0.014</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1033</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.6848</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5725</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2623</v>
+        <v>-2.1402</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6898</v>
+        <v>2.9351</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2677</v>
@@ -1000,13 +1000,13 @@
         <v>2.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9654</v>
+        <v>2.3328</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8277</v>
+        <v>1.9498</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1378</v>
+        <v>0.3831</v>
       </c>
       <c r="V7" t="n">
         <v>0.894</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.322</v>
+        <v>-0.3415</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.6053</v>
+        <v>-0.3598</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2833</v>
+        <v>0.0183</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1153</v>
+        <v>-0.2988</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.9049</v>
+        <v>0.061</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7897</v>
+        <v>-0.3598</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5512</v>
+        <v>-0.6267</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8784</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3271</v>
+        <v>-0.6267</v>
       </c>
       <c r="M8" t="n">
-        <v>0.436</v>
+        <v>0.3279</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0266</v>
+        <v>0.061</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4626</v>
+        <v>0.2669</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3582</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2985</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5399</v>
+        <v>-0.0426</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1138</v>
+        <v>0.2669</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5738</v>
+        <v>-0.3095</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.025</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9398</v>
+        <v>-1.8397</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="F9" t="n">
         <v>-1.0179</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0606</v>
+        <v>0.0395</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0606</v>
+        <v>0.0395</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4347</v>
+        <v>-2.4733</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7562</v>
+        <v>0.2052</v>
       </c>
       <c r="F10" t="n">
         <v>-2.6785</v>
@@ -1234,10 +1234,10 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3881</v>
+        <v>0.5734</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5204</v>
+        <v>0.441</v>
       </c>
       <c r="U10" t="n">
         <v>0.1324</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5819</v>
+        <v>-4.1754</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.967</v>
+        <v>-1.506</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6149</v>
+        <v>-2.6694</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7528</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6187</v>
+        <v>1.0251</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0595</v>
+        <v>0.4015</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6781</v>
+        <v>0.6236</v>
       </c>
       <c r="V11" t="n">
         <v>-3.6716</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.504400000000001</v>
+        <v>6.110000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3205</v>
+        <v>2.926199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1838</v>
+        <v>3.183800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-6.8945</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.310899999999999</v>
+        <v>-6.3109</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5838999999999994</v>
+        <v>-0.5839000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.9571</v>
+        <v>-3.957100000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-1.4828</v>
@@ -1390,13 +1390,13 @@
         <v>17.4629</v>
       </c>
       <c r="S12" t="n">
-        <v>13.3466</v>
+        <v>13.9522</v>
       </c>
       <c r="T12" t="n">
-        <v>10.5704</v>
+        <v>11.1761</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7761</v>
+        <v>2.7762</v>
       </c>
       <c r="V12" t="n">
         <v>-3.8581</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.385</v>
+        <v>6.3122</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7414</v>
+        <v>4.2409</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6437</v>
+        <v>2.0713</v>
       </c>
       <c r="G13" t="n">
         <v>6.2179</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6687</v>
+        <v>-1.7415</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3779</v>
+        <v>-0.1226</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0466</v>
+        <v>-1.6189</v>
       </c>
       <c r="V13" t="n">
         <v>1.8358</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7258</v>
+        <v>4.8198</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9225</v>
+        <v>3.7223</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8033</v>
+        <v>1.0975</v>
       </c>
       <c r="G14" t="n">
         <v>4.173</v>
@@ -1546,13 +1546,13 @@
         <v>1.3582</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1471</v>
+        <v>-1.0531</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0011</v>
+        <v>-0.1991</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1482</v>
+        <v>-0.854</v>
       </c>
       <c r="V14" t="n">
         <v>1.506</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7891</v>
+        <v>1.0142</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3517</v>
+        <v>-1.4045</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5626</v>
+        <v>2.4187</v>
       </c>
       <c r="G15" t="n">
-        <v>2.782</v>
+        <v>-0.9787</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4833</v>
+        <v>-0.4688</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7013</v>
+        <v>-0.51</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7943</v>
+        <v>-1.6936</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3398</v>
+        <v>-0.3995</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5455</v>
+        <v>-1.2941</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9878</v>
+        <v>0.7149</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1435</v>
+        <v>-0.0692</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1557</v>
+        <v>0.7841</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4988</v>
+        <v>-1.213</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.544</v>
+        <v>-0.4526</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9549</v>
+        <v>-0.7604</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2821</v>
+        <v>3.0119</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0119</v>
+        <v>2.6821</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.7298</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7351</v>
+        <v>0.7652</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6047</v>
+        <v>1.2516</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3397</v>
+        <v>-0.4864</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9787</v>
+        <v>2.782</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4688</v>
+        <v>3.4833</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.51</v>
+        <v>-0.7013</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.6936</v>
+        <v>1.7943</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3995</v>
+        <v>2.3398</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2941</v>
+        <v>-0.5455</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7149</v>
+        <v>0.9878</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0692</v>
+        <v>1.1435</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7841</v>
+        <v>-0.1557</v>
       </c>
       <c r="P16" t="n">
-        <v>0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4921</v>
+        <v>-1.5228</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6528</v>
+        <v>-0.6441</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8393</v>
+        <v>-0.8787</v>
       </c>
       <c r="V16" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="W16" t="n">
         <v>3.0119</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.6821</v>
-      </c>
       <c r="X16" t="n">
-        <v>0.3299</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9778</v>
+        <v>-1.8082</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9475</v>
+        <v>-3.448</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9697</v>
+        <v>1.6398</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1225</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2135</v>
+        <v>-1.0439</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2568</v>
+        <v>-0.2437</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4703</v>
+        <v>-0.8002</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ALMENARA SANABRIAS</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7759</v>
+        <v>-2.5478</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9527</v>
+        <v>0.4291</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8233</v>
+        <v>-2.9769</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3697</v>
+        <v>-0.6829</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5522</v>
+        <v>-0.4226</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8175</v>
+        <v>-0.2603</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3347</v>
+        <v>-0.2468</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3347</v>
+        <v>-0.2925</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.035</v>
+        <v>-0.4361</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2175</v>
+        <v>-0.1302</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8175</v>
+        <v>-0.3059</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.194</v>
+        <v>-2.3284</v>
       </c>
       <c r="R18" t="n">
-        <v>0.194</v>
+        <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4062</v>
+        <v>-1.4589</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.424</v>
+        <v>-0.0076</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0177</v>
+        <v>-1.4513</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.0119</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>D. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3209</v>
+        <v>-2.603</v>
       </c>
       <c r="E19" t="n">
-        <v>0.329</v>
+        <v>-1.7525</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6499</v>
+        <v>-0.8505</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6829</v>
+        <v>-2.3697</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4226</v>
+        <v>-1.5522</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2603</v>
+        <v>-0.8175</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2468</v>
+        <v>-1.3347</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2925</v>
+        <v>-1.3347</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4361</v>
+        <v>-1.035</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1302</v>
+        <v>-0.2175</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3059</v>
+        <v>-0.8175</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3284</v>
+        <v>-0.194</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2319</v>
+        <v>-0.2333</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1077</v>
+        <v>-0.2238</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1242</v>
+        <v>-0.0095</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.0119</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0026</v>
+        <v>-4.7117</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4658</v>
+        <v>-1.3657</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5368</v>
+        <v>-3.346</v>
       </c>
       <c r="G20" t="n">
         <v>-2.064</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0729</v>
+        <v>-0.782</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6662</v>
+        <v>-0.5661</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4067</v>
+        <v>-0.2159</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4477</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0623</v>
+        <v>-4.7431</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.5578</v>
+        <v>-4.8571</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5044999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="G21" t="n">
         <v>1.9396</v>
@@ -2092,13 +2092,13 @@
         <v>2.7164</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.6153</v>
+        <v>-2.2961</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0173</v>
+        <v>-0.3166</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.598</v>
+        <v>-1.9795</v>
       </c>
       <c r="V21" t="n">
         <v>-0.894</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.504499999999999</v>
+        <v>-3.5024</v>
       </c>
       <c r="E22" t="n">
         <v>-3.1839</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3207</v>
+        <v>-0.318500000000001</v>
       </c>
       <c r="G22" t="n">
         <v>6.8947</v>
@@ -2140,7 +2140,7 @@
         <v>6.310700000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5838</v>
+        <v>0.5838000000000004</v>
       </c>
       <c r="J22" t="n">
         <v>2.9375</v>
@@ -2170,13 +2170,13 @@
         <v>14.5524</v>
       </c>
       <c r="S22" t="n">
-        <v>-13.3465</v>
+        <v>-11.3446</v>
       </c>
       <c r="T22" t="n">
         <v>-2.7762</v>
       </c>
       <c r="U22" t="n">
-        <v>-10.5705</v>
+        <v>-8.5684</v>
       </c>
       <c r="V22" t="n">
         <v>3.8583</v>
